--- a/debug/judgements_q_sty_swi/excel_overviews/gpt-4.1_vs_Llama-3.1-8B-Instruct/Qwen3-4B-Instruct-2507/default/total_votes_file.xlsx
+++ b/debug/judgements_q_sty_swi/excel_overviews/gpt-4.1_vs_Llama-3.1-8B-Instruct/Qwen3-4B-Instruct-2507/default/total_votes_file.xlsx
@@ -436,10 +436,10 @@
         <v>120</v>
       </c>
       <c r="E2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H2">
         <v>426</v>
@@ -450,13 +450,13 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>281</v>
+        <v>274</v>
       </c>
       <c r="D3">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G3">
         <v>11</v>
